--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotTableWithNoneTheme/outputfile.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotTableWithNoneTheme/outputfile.xlsx
@@ -74,10 +74,10 @@
     <x:t>Row Labels</x:t>
   </x:si>
   <x:si>
+    <x:t>Grand Total</x:t>
+  </x:si>
+  <x:si>
     <x:t>(blank)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grand Total</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1160,10 +1160,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="s">
         <x:v>16</x:v>
-      </x:c>
-      <x:c r="C2" s="6" t="s">
-        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1223,7 +1223,7 @@
     </x:row>
     <x:row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <x:c r="A8" s="13" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B8" s="14"/>
       <x:c r="C8" s="15"/>

--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotTableWithNoneTheme/outputfile.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotTableWithNoneTheme/outputfile.xlsx
@@ -824,51 +824,49 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr codeName="Sheet1">
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
+  <x:sheetPr codeName="Sheet1"/>
   <x:dimension ref="A1:F17"/>
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.570312" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="8.855469" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="19.425781" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="10.710938" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="10.285156" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="12.710938" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9.570312" customWidth="1"/>
+    <x:col min="2" max="2" width="8.855469" customWidth="1"/>
+    <x:col min="3" max="3" width="19.425781" customWidth="1"/>
+    <x:col min="4" max="4" width="10.710938" customWidth="1"/>
+    <x:col min="5" max="5" width="10.285156" customWidth="1"/>
+    <x:col min="6" max="6" width="12.710938" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <x:c r="A1" s="0" t="s">
+      <x:c r="A1" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B1" s="0" t="s">
+      <x:c r="B1" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C1" s="0" t="s">
+      <x:c r="C1" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D1" s="0" t="s">
+      <x:c r="D1" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E1" s="0" t="s">
+      <x:c r="E1" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F1" s="0" t="s">
+      <x:c r="F1" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <x:c r="A2" s="0" t="s">
+      <x:c r="A2" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B2" s="0">
+      <x:c r="B2">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="C2" s="0">
+      <x:c r="C2">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="D2" s="0">
+      <x:c r="D2">
         <x:v>60.2</x:v>
       </x:c>
       <x:c r="F2" s="1">
@@ -876,16 +874,16 @@
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <x:c r="A3" s="0" t="s">
+      <x:c r="A3" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B3" s="0">
+      <x:c r="B3">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="C3" s="0">
+      <x:c r="C3">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="D3" s="0">
+      <x:c r="D3">
         <x:v>50.42</x:v>
       </x:c>
       <x:c r="F3" s="1">
@@ -893,16 +891,16 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <x:c r="A4" s="0" t="s">
+      <x:c r="A4" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B4" s="0">
+      <x:c r="B4">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="C4" s="0">
+      <x:c r="C4">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="D4" s="0">
+      <x:c r="D4">
         <x:v>22.12</x:v>
       </x:c>
       <x:c r="F4" s="1">
@@ -910,16 +908,16 @@
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <x:c r="A5" s="0" t="s">
+      <x:c r="A5" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B5" s="0">
+      <x:c r="B5">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="C5" s="0">
+      <x:c r="C5">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="D5" s="0">
+      <x:c r="D5">
         <x:v>89.99</x:v>
       </x:c>
       <x:c r="F5" s="1">
@@ -927,16 +925,16 @@
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <x:c r="A6" s="0" t="s">
+      <x:c r="A6" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B6" s="0">
+      <x:c r="B6">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="C6" s="0">
+      <x:c r="C6">
         <x:v>225</x:v>
       </x:c>
-      <x:c r="D6" s="0">
+      <x:c r="D6">
         <x:v>70</x:v>
       </x:c>
       <x:c r="F6" s="1">
@@ -944,16 +942,16 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <x:c r="A7" s="0" t="s">
+      <x:c r="A7" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B7" s="0">
+      <x:c r="B7">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="C7" s="0">
+      <x:c r="C7">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="D7" s="0">
+      <x:c r="D7">
         <x:v>75.33</x:v>
       </x:c>
       <x:c r="F7" s="1">
@@ -961,16 +959,16 @@
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <x:c r="A8" s="0" t="s">
+      <x:c r="A8" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B8" s="0">
+      <x:c r="B8">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="C8" s="0">
+      <x:c r="C8">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="D8" s="0">
+      <x:c r="D8">
         <x:v>10.24</x:v>
       </x:c>
       <x:c r="F8" s="1">
@@ -978,16 +976,16 @@
       </x:c>
     </x:row>
     <x:row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <x:c r="A9" s="0" t="s">
+      <x:c r="A9" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B9" s="0">
+      <x:c r="B9">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="C9" s="0">
+      <x:c r="C9">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="D9" s="0">
+      <x:c r="D9">
         <x:v>33.33</x:v>
       </x:c>
       <x:c r="F9" s="1">
@@ -995,16 +993,16 @@
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <x:c r="A10" s="0" t="s">
+      <x:c r="A10" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B10" s="0">
+      <x:c r="B10">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="C10" s="0">
+      <x:c r="C10">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="D10" s="0">
+      <x:c r="D10">
         <x:v>25</x:v>
       </x:c>
       <x:c r="F10" s="1">
@@ -1012,31 +1010,31 @@
       </x:c>
     </x:row>
     <x:row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <x:c r="A11" s="0" t="s">
+      <x:c r="A11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B11" s="0">
+      <x:c r="B11">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="C11" s="0">
+      <x:c r="C11">
         <x:v>394</x:v>
       </x:c>
-      <x:c r="D11" s="0">
+      <x:c r="D11">
         <x:v>-20.24</x:v>
       </x:c>
       <x:c r="F11" s="2"/>
     </x:row>
     <x:row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <x:c r="A12" s="0" t="s">
+      <x:c r="A12" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B12" s="0">
+      <x:c r="B12">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="C12" s="0">
+      <x:c r="C12">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="D12" s="0">
+      <x:c r="D12">
         <x:v>60</x:v>
       </x:c>
       <x:c r="F12" s="1">
@@ -1044,16 +1042,16 @@
       </x:c>
     </x:row>
     <x:row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <x:c r="A13" s="0" t="s">
+      <x:c r="A13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B13" s="0">
+      <x:c r="B13">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="C13" s="0">
+      <x:c r="C13">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="D13" s="0">
+      <x:c r="D13">
         <x:v>24.76</x:v>
       </x:c>
       <x:c r="F13" s="1">
@@ -1061,16 +1059,16 @@
       </x:c>
     </x:row>
     <x:row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <x:c r="A14" s="0" t="s">
+      <x:c r="A14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B14" s="0">
+      <x:c r="B14">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="C14" s="0">
+      <x:c r="C14">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="D14" s="0">
+      <x:c r="D14">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F14" s="1">
@@ -1078,16 +1076,16 @@
       </x:c>
     </x:row>
     <x:row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <x:c r="A15" s="0" t="s">
+      <x:c r="A15" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B15" s="0">
+      <x:c r="B15">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="C15" s="0">
+      <x:c r="C15">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="D15" s="0">
+      <x:c r="D15">
         <x:v>5.19</x:v>
       </x:c>
       <x:c r="F15" s="1">
@@ -1095,16 +1093,16 @@
       </x:c>
     </x:row>
     <x:row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <x:c r="A16" s="0" t="s">
+      <x:c r="A16" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B16" s="0">
+      <x:c r="B16">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="C16" s="0">
+      <x:c r="C16">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="D16" s="0">
+      <x:c r="D16">
         <x:v>44.2</x:v>
       </x:c>
       <x:c r="F16" s="1">
@@ -1112,21 +1110,18 @@
       </x:c>
     </x:row>
     <x:row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <x:c r="A17" s="0" t="s">
+      <x:c r="A17" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C17" s="0">
+      <x:c r="C17">
         <x:v>255</x:v>
       </x:c>
-      <x:c r="D17" s="0">
+      <x:c r="D17">
         <x:v>18.4</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
   <x:tableParts count="1">
     <x:tablePart r:id="rId1"/>
   </x:tableParts>
@@ -1135,15 +1130,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr codeName="Sheet3">
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
+  <x:sheetPr codeName="Sheet3"/>
   <x:dimension ref="A1:C8"/>
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:cols>
-    <x:col min="1" max="1" width="37.425781" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="2" max="2" width="16.285156" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="3" max="3" width="11.140625" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="1" max="1" width="37.425781" bestFit="1" customWidth="1"/>
+    <x:col min="2" max="2" width="16.285156" bestFit="1" customWidth="1"/>
+    <x:col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1229,10 +1222,6 @@
       <x:c r="C8" s="15"/>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotTableWithNoneTheme/outputfile.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotTableWithNoneTheme/outputfile.xlsx
@@ -828,12 +828,12 @@
   <x:dimension ref="A1:F17"/>
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.570312" customWidth="1"/>
-    <x:col min="2" max="2" width="8.855469" customWidth="1"/>
-    <x:col min="3" max="3" width="19.425781" customWidth="1"/>
-    <x:col min="4" max="4" width="10.710938" customWidth="1"/>
-    <x:col min="5" max="5" width="10.285156" customWidth="1"/>
-    <x:col min="6" max="6" width="12.710938" customWidth="1"/>
+    <x:col min="1" max="1" width="9.5703125" customWidth="1"/>
+    <x:col min="2" max="2" width="8.85546875" customWidth="1"/>
+    <x:col min="3" max="3" width="19.42578125" customWidth="1"/>
+    <x:col min="4" max="4" width="10.7109375" customWidth="1"/>
+    <x:col min="5" max="5" width="10.28515625" customWidth="1"/>
+    <x:col min="6" max="6" width="12.7109375" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1134,8 +1134,8 @@
   <x:dimension ref="A1:C8"/>
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:cols>
-    <x:col min="1" max="1" width="37.425781" bestFit="1" customWidth="1"/>
-    <x:col min="2" max="2" width="16.285156" bestFit="1" customWidth="1"/>
+    <x:col min="1" max="1" width="37.42578125" bestFit="1" customWidth="1"/>
+    <x:col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
     <x:col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>

--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotTableWithNoneTheme/outputfile.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotTableWithNoneTheme/outputfile.xlsx
@@ -1164,10 +1164,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B3" s="8">
-        <x:v>1.20814479638009</x:v>
+        <x:v>1.2081447963800904</x:v>
       </x:c>
       <x:c r="C3" s="9">
-        <x:v>1.20814479638009</x:v>
+        <x:v>1.2081447963800904</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1175,10 +1175,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B4" s="11">
-        <x:v>1.54977375565611</x:v>
+        <x:v>1.5497737556561086</x:v>
       </x:c>
       <x:c r="C4" s="12">
-        <x:v>1.54977375565611</x:v>
+        <x:v>1.5497737556561086</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1197,10 +1197,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B6" s="11">
-        <x:v>1.82126696832579</x:v>
+        <x:v>1.8212669683257918</x:v>
       </x:c>
       <x:c r="C6" s="12">
-        <x:v>1.82126696832579</x:v>
+        <x:v>1.8212669683257918</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1208,10 +1208,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B7" s="11">
-        <x:v>1.70814479638009</x:v>
+        <x:v>1.7081447963800904</x:v>
       </x:c>
       <x:c r="C7" s="12">
-        <x:v>1.70814479638009</x:v>
+        <x:v>1.7081447963800904</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3" x14ac:dyDescent="0.25">
